--- a/results/momentum_merged_2026-09-29.xlsx
+++ b/results/momentum_merged_2026-09-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AERT</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ONCO</t>
+          <t>NEON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACGLO</t>
+          <t>AEHL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>COSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,1300 +473,1300 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RDNW</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>FJDIU</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>ACRV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RFAMU</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BLNK</t>
+          <t>ADI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKK</t>
+          <t>AUUD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADAMG</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>AERT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BRKRP</t>
+          <t>CAMT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COLA</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>QSI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GGR</t>
+          <t>COLA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>SDEV</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DOMH</t>
+          <t>AIIA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>CRUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALVO</t>
+          <t>SXTP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FAC</t>
+          <t>ALP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>GCDT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALZN</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IQST</t>
+          <t>ARW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MEDS</t>
+          <t>GNLN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>XRPN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MWC</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OCC</t>
+          <t>KLAC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRSN</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>MSS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QMLS</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>MWC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>PDC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PCAP</t>
+          <t>PLAB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>POM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>RDNW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>AVAT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>RXT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SONM</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BATRA</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WSHP</t>
+          <t>SPHL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>BCHT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>BCSS</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BDSX</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BFRG</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BHFAL</t>
+          <t>BNR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>BURU</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BNGO</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CBAT</t>
+          <t>CDRO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CCNEP</t>
+          <t>CEVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CHOW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CHSCO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHEC</t>
+          <t>CLGN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHOW</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>COIN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CNTN</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>CPOP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>CURX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CPOP</t>
+          <t>DGII</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>DIOD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>DJCO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DJT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>DXPE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CURI</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CWD</t>
+          <t>EGBN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DJCO</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>FBLA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ECX</t>
+          <t>FSBW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EDTK</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>GLND</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>GRI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>GTBP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GYRE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>HITI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>HQI</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>HSDT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEGGL</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>IFBD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GLSI</t>
+          <t>INAB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>IOND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>IOSP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GTBP</t>
+          <t>KAZR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GYRE</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KMDA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>LTRX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IOND</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>MCHPP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MRAM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>NNBR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>NTNX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>NTRBW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LTRX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>NVEC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>NWGL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MDWD</t>
+          <t>NXXT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MIRA</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>ORBS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>OXBR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>OXLCZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NSTS</t>
+          <t>PAAI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>PCAP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>PGEN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>PLXS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NXXT</t>
+          <t>POWW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OCCIN</t>
+          <t>PSHG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>PXLW</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OXLCI</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>QTRX</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PAAI</t>
+          <t>RCMT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PACH</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>RMTI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PFLA</t>
+          <t>RVSB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PGEN</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PHOS</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PLPC</t>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SBMT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SGHT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PPSI</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>QNTM</t>
+          <t>SLAB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SLMT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>SONO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RDIB</t>
+          <t>SRZN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SSYS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>STRF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RILYN</t>
+          <t>SUIG</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RNW</t>
+          <t>SVCO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>SVIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SVIAW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>SVRN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>TCPC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>TER</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOPH</t>
+          <t>TITN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SQFTP</t>
+          <t>TKNO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>TWAV</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>VICR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>XCBE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>AMPH</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TELO</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>RENX</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TLACU</t>
+          <t>PRTH</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TONT</t>
+          <t>YDES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TONX</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TRLV</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>REFR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XXI</t>
+          <t>MXL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EGHT</t>
+          <t>AIFA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OUST</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>PDFS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>GGR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>CRCT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>SECZ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>SILC</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>TNMG</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>SHPH</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ARQQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>XXI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>KBSX</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SECZ</t>
+          <t>TAYD</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>OESX</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>WSHP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IMOS</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MREO</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>ILMN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BHFAM</t>
+          <t>COHU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ARQQ</t>
+          <t>MREO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GLND</t>
+          <t>MLCI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>MASS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MRAM</t>
+          <t>RGEN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BATRK</t>
+          <t>LSCC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>FIRY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KBSX</t>
+          <t>STKE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1776,93 +1776,9 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>STKE</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>KLIC</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>REFR</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>USDEW</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BNR</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>SVCO</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>MXL</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>SHPH</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>PRTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>TKNO</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>SXTP</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>SUIG</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>BLLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>FORM</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>EEIQ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>TJGC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
